--- a/FigafJiraIntegration/IntegrationFlow/Update_Figaf_Transport_from_Jira/Documentation.xlsx
+++ b/FigafJiraIntegration/IntegrationFlow/Update_Figaf_Transport_from_Jira/Documentation.xlsx
@@ -368,7 +368,7 @@
     <t>Address</t>
   </si>
   <si>
-    <t>sampledev(cpi-trial-alex)-&gt;sampleqa(cpi-trial-alex)</t>
+    <t>sampledev(trial-cpi-alex)-&gt;sampleqa(trial-cpi-alex)</t>
   </si>
   <si>
     <t>sampledev</t>
@@ -407,25 +407,25 @@
     <t>externalTicketIds</t>
   </si>
   <si>
+    <t>Script</t>
+  </si>
+  <si>
+    <t>parse_issue_key.groovy</t>
+  </si>
+  <si>
+    <t>2026-07-13 07:12 AM</t>
+  </si>
+  <si>
+    <t>get_error.groovy</t>
+  </si>
+  <si>
+    <t>parse_transport_id.groovy</t>
+  </si>
+  <si>
     <t>IFlow Configuration</t>
   </si>
   <si>
     <t>Update_Figaf_Transport_from_Jira iflow configuration.json</t>
-  </si>
-  <si>
-    <t>2026-07-13 07:12 AM</t>
-  </si>
-  <si>
-    <t>Script</t>
-  </si>
-  <si>
-    <t>parse_transport_id.groovy</t>
-  </si>
-  <si>
-    <t>get_error.groovy</t>
-  </si>
-  <si>
-    <t>parse_issue_key.groovy</t>
   </si>
 </sst>
 </file>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="6" ht="15.0" customHeight="true">
       <c r="A6" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>123</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="7" ht="15.0" customHeight="true">
       <c r="A7" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>123</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="8" ht="15.0" customHeight="true">
       <c r="A8" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>127</v>
